--- a/Usage/Output/stats_FanIn.xlsx
+++ b/Usage/Output/stats_FanIn.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,26 +451,1482 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>scipy.stats._multivariate.multivariate_t_gen._logpdf</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>9636</v>
+      </c>
+      <c r="D2" t="n">
+        <v>9639</v>
+      </c>
+      <c r="E2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.random_ortho</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>scipy.stats._multivariate.wishart_gen._rvs</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>6118</v>
+      </c>
+      <c r="D4" t="n">
+        <v>16</v>
+      </c>
+      <c r="E4" t="n">
+        <v>44</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>scipy.stats._mannwhitneyu._MWU.build_u_freqs_array</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4270</v>
+      </c>
+      <c r="D5" t="n">
+        <v>920</v>
+      </c>
+      <c r="E5" t="n">
+        <v>36</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/_mannwhitneyu.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>scipy.stats._mstats_extras._hd_1D</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1374</v>
+      </c>
+      <c r="D6" t="n">
+        <v>227</v>
+      </c>
+      <c r="E6" t="n">
+        <v>29</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/_mstats_extras.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>scipy._external.array_api_compat._internal.wrapped_f</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>@</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>194</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1221909</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/subprojects/array_api_compat/array_api_compat/array_api_compat/_internal.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>scipy.stats._multivariate._PSD.pinv</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>124</v>
+      </c>
+      <c r="D8" t="n">
+        <v>124</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>scipy.stats._multivariate.matrix_normal_gen._logpdf</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>117</v>
+      </c>
+      <c r="D9" t="n">
+        <v>117</v>
+      </c>
+      <c r="E9" t="n">
+        <v>37</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>scipy.stats._multivariate.wishart_gen._logpdf</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>trace</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>106</v>
+      </c>
+      <c r="D10" t="n">
+        <v>28</v>
+      </c>
+      <c r="E10" t="n">
+        <v>45</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestOrthoGroup.test_det_and_ortho</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>100</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestOrthoGroup.test_det_and_ortho</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>det</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>100</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>14</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>scipy.stats._multivariate.multivariate_normal_gen.rvs</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>97</v>
+      </c>
+      <c r="D13" t="n">
+        <v>150</v>
+      </c>
+      <c r="E13" t="n">
+        <v>36</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>scipy.stats._qmc.Sobol._scramble</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>dot</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>66</v>
+      </c>
+      <c r="D14" t="n">
+        <v>66</v>
+      </c>
+      <c r="E14" t="n">
+        <v>17</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/_qmc.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestCovariance.test_mvn_with_covariance</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>56</v>
+      </c>
+      <c r="D15" t="n">
+        <v>80</v>
+      </c>
+      <c r="E15" t="n">
+        <v>39</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>scipy.stats._kde.gaussian_kde.resample</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>52</v>
+      </c>
+      <c r="D16" t="n">
+        <v>28</v>
+      </c>
+      <c r="E16" t="n">
+        <v>34</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/_kde.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>scipy.stats._multivariate.special_ortho_group_gen.rvs</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>det</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>45</v>
+      </c>
+      <c r="D17" t="n">
+        <v>49</v>
+      </c>
+      <c r="E17" t="n">
+        <v>23</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>scipy.stats._multivariate.multivariate_t_gen.rvs</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>44</v>
+      </c>
+      <c r="D18" t="n">
+        <v>22</v>
+      </c>
+      <c r="E18" t="n">
+        <v>46</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestSpecialOrthoGroup.test_det_and_ortho</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>30</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>13</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestSpecialOrthoGroup.test_det_and_ortho</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>det</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>30</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>13</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestUnitaryGroup.test_unitarity</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>30</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>8</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestMultivariateNormal.test_degenerate_distributions</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>24</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>51</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>scipy.stats._multivariate.random_correlation_gen.rvs</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>20</v>
+      </c>
+      <c r="D23" t="n">
+        <v>17</v>
+      </c>
+      <c r="E23" t="n">
+        <v>39</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestVonMises_Fisher.test_samples</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>16</v>
+      </c>
+      <c r="D24" t="n">
+        <v>16</v>
+      </c>
+      <c r="E24" t="n">
+        <v>13</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestVonMises_Fisher.test_fit_accuracy</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>12</v>
+      </c>
+      <c r="D25" t="n">
+        <v>12</v>
+      </c>
+      <c r="E25" t="n">
+        <v>16</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>scipy.stats._mstats_extras._mjci_1D</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>12</v>
+      </c>
+      <c r="D26" t="n">
         <v>2</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E26" t="n">
+        <v>15</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/_mstats_extras.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestCovariance.test_mvn_with_covariance_cdf</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>10</v>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="n">
+        <v>25</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestMultivariateNormal.test_degenerate_array</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>21</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestCovariance.test_mvn_with_covariance</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>inv</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>80</v>
+      </c>
+      <c r="E29" t="n">
+        <v>39</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestUniformDirection.test_samples</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>8</v>
+      </c>
+      <c r="D30" t="n">
+        <v>8</v>
+      </c>
+      <c r="E30" t="n">
+        <v>12</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestInvwishart.test_frozen</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>31</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestWishart.test_frozen</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>6</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>31</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestRandomCorrelation.test_definition</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>det</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>35</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestOrthoGroup.test_det_distribution_gh18272</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>det</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="n">
+        <v>4</v>
+      </c>
+      <c r="E34" t="n">
+        <v>12</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestRandomCorrelation.test_to_corr</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>31</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestMultivariateNormal.test_rank</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>10</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestMultivariateNormal.test_pseudodet_pinv</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>25</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestWishart.test_is_scaled_chisquared</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>34</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestWishart.test_wishart_2D_rvs</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
         <v>2</v>
       </c>
-      <c r="E2" t="n">
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>43</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestCovariance.test_mvn_with_covariance_cdf</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>inv</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="n">
+        <v>25</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestInvwishart.test_sample_mean</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>26</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestMultivariateNormal.test_large_pseudo_determinant</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>det</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>23</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_kdeoth.test_kde_2d_weighted</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>65</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_kdeoth.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestCovariance.test_covariance</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>inv</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" t="n">
+        <v>20</v>
+      </c>
+      <c r="E44" t="n">
+        <v>48</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestMultivariateNormal.test_fit_fix_mean</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>27</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestCovariance.test_factories</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>inv</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" t="n">
+        <v>13</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_kdeoth.test_singular_data_covariance_gh10205</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>13</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_kdeoth.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_kdeoth.test_seed</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>48</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_kdeoth.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_kdeoth.test_kde_2d</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>62</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_kdeoth.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestInvwishart.test_logpdf_4x4</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>trace</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>23</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_kdeoth.test_fewer_points_than_dimensions_gh17436</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>11</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_kdeoth.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestOrthoGroup.test_reproducibility</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>det</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>12</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestMultivariateNormal.test_large_sample</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>16</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestInvwishart.test_invwishart_2D_rvs</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>45</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.matrix_divergence</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>trace</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>9</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestMultivariateNormal.test_broadcasting</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>23</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestMultivariateNormal.test_entropy</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
         <v>17</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/_qmc.py</t>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>scipy.stats.tests.test_multivariate.TestMultivariateNormal.test_fit_fix_cov</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>dot</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="n">
+        <v>26</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>/Users/muyeedahmed/Desktop/Gitcode/ForkedLibrary/scipy/scipy/stats/tests/test_multivariate.py</t>
         </is>
       </c>
     </row>
